--- a/data/STUDENT 1.xlsx
+++ b/data/STUDENT 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Student\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA271E1-5A5C-4CF6-BAB1-CB8363335BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9547ABB5-C7BD-4B6F-81F6-671E9504629D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -575,6 +575,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -590,10 +594,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1436,7 +1436,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>445</v>
       </c>
-      <c r="L2" s="22">
+      <c r="L2" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>63.571428571428569</v>
       </c>
@@ -1477,7 +1477,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>412</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>58.857142857142854</v>
       </c>
@@ -1518,7 +1518,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>549</v>
       </c>
-      <c r="L4" s="22">
+      <c r="L4" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>78.428571428571431</v>
       </c>
@@ -1559,7 +1559,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>541</v>
       </c>
-      <c r="L5" s="22">
+      <c r="L5" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>77.285714285714292</v>
       </c>
@@ -1600,7 +1600,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>439</v>
       </c>
-      <c r="L6" s="22">
+      <c r="L6" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>62.714285714285715</v>
       </c>
@@ -1641,7 +1641,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>455</v>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>65</v>
       </c>
@@ -1682,7 +1682,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>494</v>
       </c>
-      <c r="L8" s="22">
+      <c r="L8" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>70.571428571428569</v>
       </c>
@@ -1723,7 +1723,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>483</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>69</v>
       </c>
@@ -1764,7 +1764,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>500</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>71.428571428571431</v>
       </c>
@@ -1805,7 +1805,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>482</v>
       </c>
-      <c r="L11" s="22">
+      <c r="L11" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>68.857142857142861</v>
       </c>
@@ -1846,7 +1846,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>461</v>
       </c>
-      <c r="L12" s="22">
+      <c r="L12" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>65.857142857142861</v>
       </c>
@@ -1887,7 +1887,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>497</v>
       </c>
-      <c r="L13" s="22">
+      <c r="L13" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>71</v>
       </c>
@@ -1937,7 +1937,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>475</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>67.857142857142861</v>
       </c>
@@ -1987,7 +1987,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>488</v>
       </c>
-      <c r="L15" s="22">
+      <c r="L15" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>69.714285714285708</v>
       </c>
@@ -2037,7 +2037,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>438</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>62.571428571428569</v>
       </c>
@@ -2087,7 +2087,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>470</v>
       </c>
-      <c r="L17" s="22">
+      <c r="L17" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>67.142857142857139</v>
       </c>
@@ -2137,7 +2137,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>462</v>
       </c>
-      <c r="L18" s="22">
+      <c r="L18" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>66</v>
       </c>
@@ -2178,7 +2178,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>501</v>
       </c>
-      <c r="L19" s="22">
+      <c r="L19" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>71.571428571428569</v>
       </c>
@@ -2219,7 +2219,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>498</v>
       </c>
-      <c r="L20" s="22">
+      <c r="L20" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>71.142857142857139</v>
       </c>
@@ -2260,7 +2260,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>421</v>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>60.142857142857146</v>
       </c>
@@ -2301,7 +2301,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>513</v>
       </c>
-      <c r="L22" s="22">
+      <c r="L22" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>73.285714285714292</v>
       </c>
@@ -2342,7 +2342,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>500</v>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>71.428571428571431</v>
       </c>
@@ -2383,7 +2383,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>548</v>
       </c>
-      <c r="L24" s="22">
+      <c r="L24" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>78.285714285714292</v>
       </c>
@@ -2424,7 +2424,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>488</v>
       </c>
-      <c r="L25" s="22">
+      <c r="L25" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>69.714285714285708</v>
       </c>
@@ -2465,7 +2465,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>538</v>
       </c>
-      <c r="L26" s="22">
+      <c r="L26" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>76.857142857142861</v>
       </c>
@@ -2506,7 +2506,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>444</v>
       </c>
-      <c r="L27" s="22">
+      <c r="L27" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>63.428571428571431</v>
       </c>
@@ -2547,7 +2547,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>425</v>
       </c>
-      <c r="L28" s="22">
+      <c r="L28" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>60.714285714285715</v>
       </c>
@@ -2588,7 +2588,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>471</v>
       </c>
-      <c r="L29" s="22">
+      <c r="L29" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>67.285714285714292</v>
       </c>
@@ -2629,7 +2629,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>539</v>
       </c>
-      <c r="L30" s="22">
+      <c r="L30" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>77</v>
       </c>
@@ -2670,7 +2670,7 @@
         <f>SUM(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>504</v>
       </c>
-      <c r="L31" s="22">
+      <c r="L31" s="17">
         <f>AVERAGE(Table1[[#This Row],[MATHS]:[GEO]])</f>
         <v>72</v>
       </c>
@@ -2816,51 +2816,51 @@
     </row>
     <row r="3" spans="2:13" ht="36" customHeight="1">
       <c r="B3" s="5"/>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
     </row>
     <row r="4" spans="2:13" ht="15.75" customHeight="1">
       <c r="B4" s="5"/>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
     </row>
     <row r="5" spans="2:13" ht="28.5" customHeight="1">
       <c r="B5" s="5"/>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="5"/>
@@ -3019,10 +3019,10 @@
         <v>V.Good</v>
       </c>
       <c r="I13" s="4"/>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -3194,7 +3194,7 @@
       <c r="G20" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="H20" s="21">
+      <c r="H20" s="16">
         <f>AVERAGE(F12:F18)</f>
         <v>71.428571428571431</v>
       </c>
@@ -3371,15 +3371,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F86D39A355080C45AB74C82FF1E3E82A" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2dad8da38e69b64d21c305678dae0be7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e0a9b9c-4ed8-4e9f-8162-c5b27aabdd60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="be9a6167c0c2a6724675cfc81f59e3cf" ns2:_="">
     <xsd:import namespace="6e0a9b9c-4ed8-4e9f-8162-c5b27aabdd60"/>
@@ -3541,6 +3532,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -3548,14 +3548,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{866154E7-A51F-4A14-BCBF-5616579110CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F821F9B-B1E0-40B8-A79F-B7E2377391BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3573,6 +3565,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{866154E7-A51F-4A14-BCBF-5616579110CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED310749-3EFE-4291-B98E-B2C89E47D4CF}">
   <ds:schemaRefs>
